--- a/ipo-analysis/companies/m-k-sons-fine-jewels-ltd/M_K_SONS_FINE_JEWELS_LTD_03_Valuation.xlsx
+++ b/ipo-analysis/companies/m-k-sons-fine-jewels-ltd/M_K_SONS_FINE_JEWELS_LTD_03_Valuation.xlsx
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>481.095</v>
+        <v>538.73</v>
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>64.25700000000001</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="C28" s="15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>38.887</v>
+        <v>51.79</v>
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C30" s="15" t="n">
-        <v>145.418</v>
+        <v>168.01</v>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>64.604</v>
+        <v>68.44</v>
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>215.405</v>
+        <v>225</v>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C34" s="15" t="n">
-        <v>2.847</v>
+        <v>3</v>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
@@ -2148,17 +2148,17 @@
         <v/>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>Revenue Rs 24.91 / 217.32 / 351.28 cr FY23-25 and Rs 360.82 cr in 9M FY26 (Rs 481.10 cr annualised, the base year here) (p. 227); part of the growth is gold-price inflation and the merged proprietorship (p. 64 of MD&amp;A, p. 189). The issue funds Rs 151.51 cr of inventory for a new Maharashtra showroom and an expanded Ahmedabad showroom in FY27 (p. 91). Neutral 20-25% in the first two years as the showrooms open, then 10-18%; Bear 7-12%; Bull 30%+.</t>
+          <t>Revenue Rs 217.32 / 351.28 / 538.73 cr FY24-26 (+62%, +53%; FY26 from the RHP via trackers), partly gold-price inflation and the full year of the merged proprietorship (DRHP pp. 64, 189). The issue funds Rs 151.51 cr of inventory for a new Maharashtra showroom and an expanded Ahmedabad showroom in FY27 (DRHP p. 91). Neutral 18% / 22% as the showrooms open, then 16% / 12% / 10%; Bear 6-10%; Bull 26-28%.</t>
         </is>
       </c>
     </row>
@@ -2173,13 +2173,13 @@
         <v/>
       </c>
       <c r="E68" s="16" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
@@ -2198,13 +2198,13 @@
         <v/>
       </c>
       <c r="E69" s="16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>0.12</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H70" s="20" t="inlineStr">
         <is>
@@ -2273,17 +2273,17 @@
         <v/>
       </c>
       <c r="E72" s="16" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>0.11</v>
+        <v>0.125</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H72" s="20" t="inlineStr">
         <is>
-          <t>EBITDA (issuer KPI: PBT + finance cost + D&amp;A - other income) 9.11% / 5.92% / 10.98% FY23-25 and 13.36% in 9M FY26 (p. 101), helped by gold-price gains on inventory. Neutral 11% (FY25 level); Bear 8.5%; Bull 13%.</t>
+          <t>EBITDA margin 5.92% / 10.98% / 15.39% FY24-26 (FY26 EBITDA Rs 82.93 cr, RHP via trackers), lifted by rising gold prices on unhedged inventory. Neutral 12.5% (between FY25 and FY26); Bear 9.5%; Bull 15% (FY26 held).</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2298,17 @@
         <v/>
       </c>
       <c r="E73" s="16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="H73" s="20" t="inlineStr">
         <is>
-          <t>Inventory + receivables - payables = 44.8% of annualised 9M FY26 revenue (p. 226); inventory days 205 (p. 101). Neutral 45%.</t>
+          <t>Estimate: Mar-26 working capital is not in the tracker data. FY26 CFO Rs 15.40 cr against PAT Rs 51.79 cr + D&amp;A ~3.5 implies a working-capital build of about Rs 40 cr, so about Rs 225 cr (42% of revenue) from Rs 185.34 cr at Mar-25 (DRHP p. 226). Neutral 42%; Bear 47%; Bull 38%.</t>
         </is>
       </c>
     </row>
